--- a/ads-weekly-report-kit/outputs/clean.xlsx
+++ b/ads-weekly-report-kit/outputs/clean.xlsx
@@ -21,16 +21,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -434,69 +422,69 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>campaign</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>adset</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>spend</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>link_clicks</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>purchase_value</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ctr</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cpc</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>cpm</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>observed_roas</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>46026</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -540,7 +528,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>46026</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -584,7 +572,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>46027</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -628,7 +616,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>46027</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -672,7 +660,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -716,7 +704,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>46028</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -760,7 +748,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -804,7 +792,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -848,7 +836,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -892,7 +880,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -936,7 +924,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -980,7 +968,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1024,7 +1012,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>46032</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1068,7 +1056,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>46032</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1126,47 +1114,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>campaign</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>spend</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>impressions</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>link_clicks</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>purchase_value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ctr</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>cpc</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>cpm</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>observed_roas</t>
         </is>
